--- a/artfynd/A 32077-2026 artfynd.xlsx
+++ b/artfynd/A 32077-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136893961</v>
       </c>
       <c r="B3" t="n">
-        <v>106494</v>
+        <v>106500</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>136902981</v>
       </c>
       <c r="B4" t="n">
-        <v>106494</v>
+        <v>106500</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32077-2026 artfynd.xlsx
+++ b/artfynd/A 32077-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136893961</v>
       </c>
       <c r="B3" t="n">
-        <v>106500</v>
+        <v>106502</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>136902981</v>
       </c>
       <c r="B4" t="n">
-        <v>106500</v>
+        <v>106502</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32077-2026 artfynd.xlsx
+++ b/artfynd/A 32077-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136893961</v>
       </c>
       <c r="B3" t="n">
-        <v>106502</v>
+        <v>106503</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>136902981</v>
       </c>
       <c r="B4" t="n">
-        <v>106502</v>
+        <v>106503</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32077-2026 artfynd.xlsx
+++ b/artfynd/A 32077-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136893961</v>
       </c>
       <c r="B3" t="n">
-        <v>106503</v>
+        <v>106509</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>136902981</v>
       </c>
       <c r="B4" t="n">
-        <v>106503</v>
+        <v>106509</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32077-2026 artfynd.xlsx
+++ b/artfynd/A 32077-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136893961</v>
       </c>
       <c r="B3" t="n">
-        <v>106509</v>
+        <v>106513</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>136902981</v>
       </c>
       <c r="B4" t="n">
-        <v>106509</v>
+        <v>106513</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32077-2026 artfynd.xlsx
+++ b/artfynd/A 32077-2026 artfynd.xlsx
@@ -1005,7 +1005,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mirjam Ideström, Jan-Erik Axelsson</t>
+          <t>Jan-Erik Axelsson, Mirjam Ideström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 32077-2026 artfynd.xlsx
+++ b/artfynd/A 32077-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136893961</v>
       </c>
       <c r="B3" t="n">
-        <v>106513</v>
+        <v>106515</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>136902981</v>
       </c>
       <c r="B4" t="n">
-        <v>106513</v>
+        <v>106515</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jan-Erik Axelsson, Mirjam Ideström</t>
+          <t>Mirjam Ideström, Jan-Erik Axelsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 32077-2026 artfynd.xlsx
+++ b/artfynd/A 32077-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136893961</v>
       </c>
       <c r="B3" t="n">
-        <v>106515</v>
+        <v>106517</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>136902981</v>
       </c>
       <c r="B4" t="n">
-        <v>106515</v>
+        <v>106517</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32077-2026 artfynd.xlsx
+++ b/artfynd/A 32077-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136893961</v>
       </c>
       <c r="B3" t="n">
-        <v>106517</v>
+        <v>106530</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>136902981</v>
       </c>
       <c r="B4" t="n">
-        <v>106517</v>
+        <v>106530</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32077-2026 artfynd.xlsx
+++ b/artfynd/A 32077-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136893949</v>
       </c>
       <c r="B2" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136893961</v>
       </c>
       <c r="B3" t="n">
-        <v>106530</v>
+        <v>106532</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>136902981</v>
       </c>
       <c r="B4" t="n">
-        <v>106530</v>
+        <v>106532</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32077-2026 artfynd.xlsx
+++ b/artfynd/A 32077-2026 artfynd.xlsx
@@ -931,11 +931,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">

--- a/artfynd/A 32077-2026 artfynd.xlsx
+++ b/artfynd/A 32077-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136893961</v>
       </c>
       <c r="B3" t="n">
-        <v>106532</v>
+        <v>106536</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>136902981</v>
       </c>
       <c r="B4" t="n">
-        <v>106532</v>
+        <v>106536</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32077-2026 artfynd.xlsx
+++ b/artfynd/A 32077-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136893949</v>
       </c>
       <c r="B2" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136893961</v>
       </c>
       <c r="B3" t="n">
-        <v>106536</v>
+        <v>106556</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>136902981</v>
       </c>
       <c r="B4" t="n">
-        <v>106536</v>
+        <v>106556</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32077-2026 artfynd.xlsx
+++ b/artfynd/A 32077-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136893961</v>
       </c>
       <c r="B3" t="n">
-        <v>106556</v>
+        <v>106557</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>136902981</v>
       </c>
       <c r="B4" t="n">
-        <v>106556</v>
+        <v>106557</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32077-2026 artfynd.xlsx
+++ b/artfynd/A 32077-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136893961</v>
       </c>
       <c r="B3" t="n">
-        <v>106557</v>
+        <v>106562</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>136902981</v>
       </c>
       <c r="B4" t="n">
-        <v>106557</v>
+        <v>106562</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32077-2026 artfynd.xlsx
+++ b/artfynd/A 32077-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136893961</v>
       </c>
       <c r="B3" t="n">
-        <v>106562</v>
+        <v>106565</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>136902981</v>
       </c>
       <c r="B4" t="n">
-        <v>106562</v>
+        <v>106565</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32077-2026 artfynd.xlsx
+++ b/artfynd/A 32077-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136893961</v>
       </c>
       <c r="B3" t="n">
-        <v>106565</v>
+        <v>106571</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>136902981</v>
       </c>
       <c r="B4" t="n">
-        <v>106565</v>
+        <v>106571</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32077-2026 artfynd.xlsx
+++ b/artfynd/A 32077-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136893961</v>
       </c>
       <c r="B3" t="n">
-        <v>106571</v>
+        <v>106572</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>136902981</v>
       </c>
       <c r="B4" t="n">
-        <v>106571</v>
+        <v>106572</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32077-2026 artfynd.xlsx
+++ b/artfynd/A 32077-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136893961</v>
       </c>
       <c r="B3" t="n">
-        <v>106572</v>
+        <v>106584</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>136902981</v>
       </c>
       <c r="B4" t="n">
-        <v>106572</v>
+        <v>106584</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32077-2026 artfynd.xlsx
+++ b/artfynd/A 32077-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136893961</v>
       </c>
       <c r="B3" t="n">
-        <v>106584</v>
+        <v>106585</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>136902981</v>
       </c>
       <c r="B4" t="n">
-        <v>106584</v>
+        <v>106585</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32077-2026 artfynd.xlsx
+++ b/artfynd/A 32077-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136893961</v>
       </c>
       <c r="B3" t="n">
-        <v>106585</v>
+        <v>106588</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>136902981</v>
       </c>
       <c r="B4" t="n">
-        <v>106585</v>
+        <v>106588</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
